--- a/data/dividends_info_20261022.xlsx
+++ b/data/dividends_info_20261022.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>40.61999893188477</v>
+        <v>39.95999908447266</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2215657369930512</v>
+        <v>0.2252252303853818</v>
       </c>
       <c r="J2" t="n">
         <v>144</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>59</v>
+        <v>57.84999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.186440677966102</v>
+        <v>1.210025961043269</v>
       </c>
       <c r="J3" t="n">
         <v>123</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.659999847412109</v>
+        <v>8.699999809265137</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6928406588590178</v>
+        <v>0.6896551875334813</v>
       </c>
       <c r="J4" t="n">
         <v>53</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.4939999878406525</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8163265147242933</v>
+        <v>0.8097166191206999</v>
       </c>
       <c r="J5" t="n">
         <v>53</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>40.61999893188477</v>
+        <v>39.95999908447266</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2215657369930512</v>
+        <v>0.2252252303853818</v>
       </c>
       <c r="J6" t="n">
         <v>53</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>50.54999923706055</v>
+        <v>49.79999923706055</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6132542130143587</v>
+        <v>0.6224899693759469</v>
       </c>
       <c r="J8" t="n">
         <v>32</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>26.46500015258789</v>
+        <v>26.1299991607666</v>
       </c>
       <c r="I9" t="n">
-        <v>1.020215372919988</v>
+        <v>1.033295096332788</v>
       </c>
       <c r="J9" t="n">
         <v>32</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25.95000076293945</v>
+        <v>24.80999946594238</v>
       </c>
       <c r="I10" t="n">
-        <v>2.273603016006881</v>
+        <v>2.378073408707304</v>
       </c>
       <c r="J10" t="n">
         <v>32</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5.889999866485596</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I12" t="n">
-        <v>3.395585815510971</v>
+        <v>3.389830453681454</v>
       </c>
       <c r="J12" t="n">
         <v>25</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>7.769999980926514</v>
+        <v>7.710000038146973</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7722007740963399</v>
+        <v>0.7782101128811465</v>
       </c>
       <c r="J14" t="n">
         <v>18</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>10.78999996185303</v>
+        <v>10.8100004196167</v>
       </c>
       <c r="I15" t="n">
-        <v>4.263206687917371</v>
+        <v>4.255318983755513</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>8.350000381469727</v>
+        <v>8.300000190734863</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7185628414239557</v>
+        <v>0.7228915496529372</v>
       </c>
       <c r="J16" t="n">
         <v>-3</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.4900000095367432</v>
+        <v>0.4939999878406525</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8163265147242933</v>
+        <v>0.8097166191206999</v>
       </c>
       <c r="J17" t="n">
         <v>-3</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>8.060000419616699</v>
+        <v>7.639999866485596</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4714639953059348</v>
+        <v>0.4973822076449854</v>
       </c>
       <c r="J19" t="n">
         <v>-24</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -1956,14 +1956,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1973,14 +1973,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1997,7 +1997,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2014,7 +2014,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2024,14 +2024,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2048,7 +2048,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2065,7 +2065,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2082,7 +2082,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2099,7 +2099,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2109,14 +2109,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2398,14 +2398,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2422,7 +2422,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2439,7 +2439,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2449,14 +2449,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2507,7 +2507,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2762,7 +2762,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2789,14 +2789,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2925,14 +2925,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2942,14 +2942,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2966,7 +2966,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3000,7 +3000,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3034,7 +3034,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3051,7 +3051,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3068,7 +3068,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3085,7 +3085,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3146,14 +3146,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3255,7 +3255,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3265,14 +3265,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3289,7 +3289,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3306,7 +3306,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3323,7 +3323,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3333,14 +3333,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3357,7 +3357,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3367,14 +3367,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3408,7 +3408,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3418,14 +3418,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3459,7 +3459,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3476,7 +3476,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3486,14 +3486,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3503,14 +3503,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3527,7 +3527,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3561,7 +3561,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3578,7 +3578,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3588,14 +3588,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3612,7 +3612,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3622,14 +3622,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3639,14 +3639,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3663,7 +3663,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3680,7 +3680,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3697,7 +3697,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3714,7 +3714,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3731,7 +3731,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3748,7 +3748,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3758,14 +3758,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3799,7 +3799,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3809,14 +3809,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3833,7 +3833,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3850,7 +3850,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3867,7 +3867,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3884,7 +3884,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3901,7 +3901,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3911,14 +3911,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3935,7 +3935,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3945,14 +3945,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3969,7 +3969,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3986,7 +3986,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4020,7 +4020,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4037,7 +4037,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4071,7 +4071,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4088,7 +4088,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4105,7 +4105,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4115,14 +4115,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4139,7 +4139,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4149,14 +4149,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4173,7 +4173,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4190,7 +4190,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4207,7 +4207,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4217,14 +4217,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4234,14 +4234,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4251,14 +4251,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4275,7 +4275,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4292,7 +4292,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4309,7 +4309,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4319,14 +4319,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4360,7 +4360,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4377,7 +4377,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4394,7 +4394,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4428,7 +4428,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4445,7 +4445,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4455,14 +4455,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4479,7 +4479,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4496,7 +4496,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4513,7 +4513,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4530,7 +4530,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4540,14 +4540,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4564,7 +4564,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4581,7 +4581,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4598,7 +4598,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4625,14 +4625,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4642,14 +4642,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4666,7 +4666,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4683,7 +4683,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4693,14 +4693,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4717,7 +4717,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4734,7 +4734,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4751,7 +4751,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4768,7 +4768,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4785,7 +4785,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4802,7 +4802,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4819,7 +4819,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4829,14 +4829,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4853,7 +4853,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4870,7 +4870,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4887,7 +4887,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4904,7 +4904,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4914,14 +4914,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4938,7 +4938,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4955,7 +4955,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4972,7 +4972,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4989,7 +4989,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5006,7 +5006,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5016,14 +5016,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5033,14 +5033,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5057,7 +5057,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5074,7 +5074,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5084,14 +5084,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5108,7 +5108,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5118,14 +5118,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5159,7 +5159,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5169,14 +5169,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5203,14 +5203,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5227,7 +5227,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5244,7 +5244,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5261,7 +5261,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5295,7 +5295,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5312,7 +5312,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5329,7 +5329,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5339,14 +5339,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5363,7 +5363,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5380,7 +5380,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5397,7 +5397,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -5424,14 +5424,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5482,7 +5482,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5499,7 +5499,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5550,7 +5550,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5560,14 +5560,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5584,7 +5584,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5594,14 +5594,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5611,14 +5611,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5628,14 +5628,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5652,7 +5652,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5696,14 +5696,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
